--- a/artfynd/A 18541-2024 artfynd.xlsx
+++ b/artfynd/A 18541-2024 artfynd.xlsx
@@ -1789,10 +1789,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118000752</v>
+        <v>118000727</v>
       </c>
       <c r="B11" t="n">
-        <v>102044</v>
+        <v>108703</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1801,47 +1801,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6037533</v>
+        <v>220299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698154</v>
+        <v>698075</v>
       </c>
       <c r="R11" t="n">
-        <v>6360659</v>
+        <v>6360628</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1874,11 +1865,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2 m hög, nedliggande, överkörd.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1910,10 +1896,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118000727</v>
+        <v>118000752</v>
       </c>
       <c r="B12" t="n">
-        <v>108703</v>
+        <v>102044</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1922,38 +1908,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220299</v>
+        <v>6037533</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>698075</v>
+        <v>698154</v>
       </c>
       <c r="R12" t="n">
-        <v>6360628</v>
+        <v>6360659</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1986,6 +1981,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2 m hög, nedliggande, överkörd.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2473,10 +2473,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118000721</v>
+        <v>118000786</v>
       </c>
       <c r="B17" t="n">
-        <v>108703</v>
+        <v>42953</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2489,34 +2489,53 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>698064</v>
+        <v>698159</v>
       </c>
       <c r="R17" t="n">
-        <v>6360663</v>
+        <v>6360654</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2549,11 +2568,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2585,10 +2599,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118000786</v>
+        <v>118000721</v>
       </c>
       <c r="B18" t="n">
-        <v>42953</v>
+        <v>108703</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2601,53 +2615,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>698159</v>
+        <v>698064</v>
       </c>
       <c r="R18" t="n">
-        <v>6360654</v>
+        <v>6360663</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2680,6 +2675,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 18541-2024 artfynd.xlsx
+++ b/artfynd/A 18541-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118000791</v>
+        <v>118000793</v>
       </c>
       <c r="B2" t="n">
         <v>42953</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698105</v>
+        <v>698144</v>
       </c>
       <c r="R2" t="n">
-        <v>6360598</v>
+        <v>6360649</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,6 +770,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Troligen nytt ex.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118000737</v>
+        <v>118000753</v>
       </c>
       <c r="B3" t="n">
-        <v>97858</v>
+        <v>108703</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,47 +818,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219862</v>
+        <v>220299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698100</v>
+        <v>698154</v>
       </c>
       <c r="R3" t="n">
-        <v>6360609</v>
+        <v>6360659</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -917,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118000782</v>
+        <v>118000746</v>
       </c>
       <c r="B4" t="n">
-        <v>42953</v>
+        <v>108703</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,56 +929,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698223</v>
+        <v>698134</v>
       </c>
       <c r="R4" t="n">
-        <v>6360767</v>
+        <v>6360639</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1043,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118000781</v>
+        <v>118000749</v>
       </c>
       <c r="B5" t="n">
-        <v>42953</v>
+        <v>97754</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101242</v>
+        <v>223591</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1083,17 +1060,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1102,13 +1069,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698223</v>
+        <v>698144</v>
       </c>
       <c r="R5" t="n">
-        <v>6360777</v>
+        <v>6360649</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1169,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118000783</v>
+        <v>118000721</v>
       </c>
       <c r="B6" t="n">
-        <v>42953</v>
+        <v>108703</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,56 +1152,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698216</v>
+        <v>698064</v>
       </c>
       <c r="R6" t="n">
-        <v>6360742</v>
+        <v>6360663</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1264,6 +1212,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1295,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118000795</v>
+        <v>118000752</v>
       </c>
       <c r="B7" t="n">
-        <v>42953</v>
+        <v>102044</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1307,45 +1260,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101242</v>
+        <v>6037533</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1354,10 +1297,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698185</v>
+        <v>698154</v>
       </c>
       <c r="R7" t="n">
-        <v>6360629</v>
+        <v>6360659</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1392,6 +1335,11 @@
           <t>2024-06-24</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2 m hög, nedliggande, överkörd.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1403,7 +1351,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Glänta i kalkbarrskog.</t>
+          <t>Barrskog med lundstarr.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1421,10 +1369,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118000831</v>
+        <v>118000790</v>
       </c>
       <c r="B8" t="n">
-        <v>57656</v>
+        <v>42953</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,35 +1381,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>101242</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1470,13 +1428,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698109</v>
+        <v>698064</v>
       </c>
       <c r="R8" t="n">
-        <v>6360613</v>
+        <v>6360688</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1537,7 +1495,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118000794</v>
+        <v>118000780</v>
       </c>
       <c r="B9" t="n">
         <v>42953</v>
@@ -1596,13 +1554,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698154</v>
+        <v>698230</v>
       </c>
       <c r="R9" t="n">
-        <v>6360659</v>
+        <v>6360781</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1663,7 +1621,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118000792</v>
+        <v>118000783</v>
       </c>
       <c r="B10" t="n">
         <v>42953</v>
@@ -1722,13 +1680,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698134</v>
+        <v>698216</v>
       </c>
       <c r="R10" t="n">
-        <v>6360639</v>
+        <v>6360742</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1789,10 +1747,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118000727</v>
+        <v>118000791</v>
       </c>
       <c r="B11" t="n">
-        <v>108703</v>
+        <v>42953</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1805,34 +1763,53 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698075</v>
+        <v>698105</v>
       </c>
       <c r="R11" t="n">
-        <v>6360628</v>
+        <v>6360598</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1896,10 +1873,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118000752</v>
+        <v>118000785</v>
       </c>
       <c r="B12" t="n">
-        <v>102044</v>
+        <v>42953</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1908,25 +1885,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6037533</v>
+        <v>101242</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1936,7 +1913,17 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1945,10 +1932,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>698154</v>
+        <v>698174</v>
       </c>
       <c r="R12" t="n">
-        <v>6360659</v>
+        <v>6360672</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1981,11 +1968,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2 m hög, nedliggande, överkörd.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2017,10 +1999,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118000749</v>
+        <v>118000792</v>
       </c>
       <c r="B13" t="n">
-        <v>97754</v>
+        <v>42953</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2029,25 +2011,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223591</v>
+        <v>101242</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2057,7 +2039,17 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2066,10 +2058,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698144</v>
+        <v>698134</v>
       </c>
       <c r="R13" t="n">
-        <v>6360649</v>
+        <v>6360639</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2133,10 +2125,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118000753</v>
+        <v>118000832</v>
       </c>
       <c r="B14" t="n">
-        <v>108703</v>
+        <v>56598</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2145,41 +2137,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>100038</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698154</v>
+        <v>698134</v>
       </c>
       <c r="R14" t="n">
-        <v>6360659</v>
+        <v>6360639</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2240,10 +2241,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118000780</v>
+        <v>118000831</v>
       </c>
       <c r="B15" t="n">
-        <v>42953</v>
+        <v>57656</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2252,25 +2253,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>101242</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2278,19 +2279,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>friflygande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2299,13 +2290,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698230</v>
+        <v>698109</v>
       </c>
       <c r="R15" t="n">
-        <v>6360781</v>
+        <v>6360613</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2366,10 +2357,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118000746</v>
+        <v>118000737</v>
       </c>
       <c r="B16" t="n">
-        <v>108703</v>
+        <v>97858</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2378,38 +2369,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>698134</v>
+        <v>698100</v>
       </c>
       <c r="R16" t="n">
-        <v>6360639</v>
+        <v>6360609</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2473,10 +2473,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118000786</v>
+        <v>118000727</v>
       </c>
       <c r="B17" t="n">
-        <v>42953</v>
+        <v>108703</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2489,53 +2489,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>698159</v>
+        <v>698075</v>
       </c>
       <c r="R17" t="n">
-        <v>6360654</v>
+        <v>6360628</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2599,10 +2580,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118000721</v>
+        <v>118000782</v>
       </c>
       <c r="B18" t="n">
-        <v>108703</v>
+        <v>42953</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2615,37 +2596,56 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>698064</v>
+        <v>698223</v>
       </c>
       <c r="R18" t="n">
-        <v>6360663</v>
+        <v>6360767</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2675,11 +2675,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2711,7 +2706,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118000793</v>
+        <v>118000794</v>
       </c>
       <c r="B19" t="n">
         <v>42953</v>
@@ -2770,10 +2765,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>698144</v>
+        <v>698154</v>
       </c>
       <c r="R19" t="n">
-        <v>6360649</v>
+        <v>6360659</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2806,11 +2801,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Troligen nytt ex.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2842,10 +2832,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118000832</v>
+        <v>118000795</v>
       </c>
       <c r="B20" t="n">
-        <v>56598</v>
+        <v>42953</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2854,35 +2844,45 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100038</v>
+        <v>101242</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>698134</v>
+        <v>698185</v>
       </c>
       <c r="R20" t="n">
-        <v>6360639</v>
+        <v>6360629</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Barrskog med lundstarr.</t>
+          <t>Glänta i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2958,7 +2958,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118000785</v>
+        <v>118000781</v>
       </c>
       <c r="B21" t="n">
         <v>42953</v>
@@ -3017,13 +3017,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>698174</v>
+        <v>698223</v>
       </c>
       <c r="R21" t="n">
-        <v>6360672</v>
+        <v>6360777</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118000790</v>
+        <v>118000786</v>
       </c>
       <c r="B22" t="n">
         <v>42953</v>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>698064</v>
+        <v>698159</v>
       </c>
       <c r="R22" t="n">
-        <v>6360688</v>
+        <v>6360654</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 18541-2024 artfynd.xlsx
+++ b/artfynd/A 18541-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118000793</v>
+        <v>118000794</v>
       </c>
       <c r="B2" t="n">
         <v>42953</v>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698144</v>
+        <v>698154</v>
       </c>
       <c r="R2" t="n">
-        <v>6360649</v>
+        <v>6360659</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,11 +770,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Troligen nytt ex.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118000753</v>
+        <v>118000749</v>
       </c>
       <c r="B3" t="n">
-        <v>108703</v>
+        <v>97756</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,38 +813,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698154</v>
+        <v>698144</v>
       </c>
       <c r="R3" t="n">
-        <v>6360659</v>
+        <v>6360649</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -913,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118000746</v>
+        <v>118000727</v>
       </c>
       <c r="B4" t="n">
-        <v>108703</v>
+        <v>108705</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -953,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698134</v>
+        <v>698075</v>
       </c>
       <c r="R4" t="n">
-        <v>6360639</v>
+        <v>6360628</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118000749</v>
+        <v>118000831</v>
       </c>
       <c r="B5" t="n">
-        <v>97754</v>
+        <v>57657</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1040,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223591</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1058,9 +1062,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1069,13 +1073,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698144</v>
+        <v>698109</v>
       </c>
       <c r="R5" t="n">
-        <v>6360649</v>
+        <v>6360613</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1136,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118000721</v>
+        <v>118000786</v>
       </c>
       <c r="B6" t="n">
-        <v>108703</v>
+        <v>42953</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,34 +1156,53 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698064</v>
+        <v>698159</v>
       </c>
       <c r="R6" t="n">
-        <v>6360663</v>
+        <v>6360654</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,11 +1235,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1266,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118000752</v>
+        <v>118000792</v>
       </c>
       <c r="B7" t="n">
-        <v>102044</v>
+        <v>42953</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,25 +1278,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6037533</v>
+        <v>101242</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1288,7 +1306,17 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1297,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698154</v>
+        <v>698134</v>
       </c>
       <c r="R7" t="n">
-        <v>6360659</v>
+        <v>6360639</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,11 +1361,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2 m hög, nedliggande, överkörd.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,7 +1392,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118000790</v>
+        <v>118000793</v>
       </c>
       <c r="B8" t="n">
         <v>42953</v>
@@ -1404,7 +1427,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1428,10 +1451,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698064</v>
+        <v>698144</v>
       </c>
       <c r="R8" t="n">
-        <v>6360688</v>
+        <v>6360649</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1464,6 +1487,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Troligen nytt ex.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,10 +1523,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118000780</v>
+        <v>118000746</v>
       </c>
       <c r="B9" t="n">
-        <v>42953</v>
+        <v>108705</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1511,56 +1539,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698230</v>
+        <v>698134</v>
       </c>
       <c r="R9" t="n">
-        <v>6360781</v>
+        <v>6360639</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1621,7 +1630,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118000783</v>
+        <v>118000785</v>
       </c>
       <c r="B10" t="n">
         <v>42953</v>
@@ -1680,13 +1689,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698216</v>
+        <v>698174</v>
       </c>
       <c r="R10" t="n">
-        <v>6360742</v>
+        <v>6360672</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1747,7 +1756,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118000791</v>
+        <v>118000782</v>
       </c>
       <c r="B11" t="n">
         <v>42953</v>
@@ -1782,7 +1791,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1806,13 +1815,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698105</v>
+        <v>698223</v>
       </c>
       <c r="R11" t="n">
-        <v>6360598</v>
+        <v>6360767</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1873,10 +1882,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118000785</v>
+        <v>118000737</v>
       </c>
       <c r="B12" t="n">
-        <v>42953</v>
+        <v>97860</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1885,45 +1894,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101242</v>
+        <v>219862</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1932,10 +1931,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>698174</v>
+        <v>698100</v>
       </c>
       <c r="R12" t="n">
-        <v>6360672</v>
+        <v>6360609</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1999,10 +1998,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118000792</v>
+        <v>118000752</v>
       </c>
       <c r="B13" t="n">
-        <v>42953</v>
+        <v>102046</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2011,25 +2010,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101242</v>
+        <v>6037533</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Garderönn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Sorbus atrata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>Hedrén &amp; J.Levin</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2039,17 +2038,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2058,10 +2047,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698134</v>
+        <v>698154</v>
       </c>
       <c r="R13" t="n">
-        <v>6360639</v>
+        <v>6360659</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2094,6 +2083,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2 m hög, nedliggande, överkörd.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2125,10 +2119,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118000832</v>
+        <v>118000721</v>
       </c>
       <c r="B14" t="n">
-        <v>56598</v>
+        <v>108705</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2137,50 +2131,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100038</v>
+        <v>220299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698134</v>
+        <v>698064</v>
       </c>
       <c r="R14" t="n">
-        <v>6360639</v>
+        <v>6360663</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2210,6 +2195,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2241,10 +2231,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118000831</v>
+        <v>118000832</v>
       </c>
       <c r="B15" t="n">
-        <v>57656</v>
+        <v>56599</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2257,21 +2247,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>100038</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2290,10 +2280,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698109</v>
+        <v>698134</v>
       </c>
       <c r="R15" t="n">
-        <v>6360613</v>
+        <v>6360639</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2357,10 +2347,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118000737</v>
+        <v>118000791</v>
       </c>
       <c r="B16" t="n">
-        <v>97858</v>
+        <v>42953</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2369,25 +2359,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219862</v>
+        <v>101242</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2397,7 +2387,17 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>698100</v>
+        <v>698105</v>
       </c>
       <c r="R16" t="n">
-        <v>6360609</v>
+        <v>6360598</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2473,10 +2473,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118000727</v>
+        <v>118000780</v>
       </c>
       <c r="B17" t="n">
-        <v>108703</v>
+        <v>42953</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2489,37 +2489,56 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>698075</v>
+        <v>698230</v>
       </c>
       <c r="R17" t="n">
-        <v>6360628</v>
+        <v>6360781</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2580,7 +2599,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118000782</v>
+        <v>118000783</v>
       </c>
       <c r="B18" t="n">
         <v>42953</v>
@@ -2639,10 +2658,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>698223</v>
+        <v>698216</v>
       </c>
       <c r="R18" t="n">
-        <v>6360767</v>
+        <v>6360742</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2706,7 +2725,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118000794</v>
+        <v>118000790</v>
       </c>
       <c r="B19" t="n">
         <v>42953</v>
@@ -2741,7 +2760,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2765,10 +2784,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>698154</v>
+        <v>698064</v>
       </c>
       <c r="R19" t="n">
-        <v>6360659</v>
+        <v>6360688</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2832,7 +2851,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118000795</v>
+        <v>118000781</v>
       </c>
       <c r="B20" t="n">
         <v>42953</v>
@@ -2867,7 +2886,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2891,13 +2910,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>698185</v>
+        <v>698223</v>
       </c>
       <c r="R20" t="n">
-        <v>6360629</v>
+        <v>6360777</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2940,7 +2959,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Glänta i kalkbarrskog.</t>
+          <t>Barrskog med lundstarr.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2958,7 +2977,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118000781</v>
+        <v>118000795</v>
       </c>
       <c r="B21" t="n">
         <v>42953</v>
@@ -2993,7 +3012,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3017,13 +3036,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>698223</v>
+        <v>698185</v>
       </c>
       <c r="R21" t="n">
-        <v>6360777</v>
+        <v>6360629</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3066,7 +3085,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Barrskog med lundstarr.</t>
+          <t>Glänta i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3084,10 +3103,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118000786</v>
+        <v>118000753</v>
       </c>
       <c r="B22" t="n">
-        <v>42953</v>
+        <v>108705</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3100,53 +3119,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>698159</v>
+        <v>698154</v>
       </c>
       <c r="R22" t="n">
-        <v>6360654</v>
+        <v>6360659</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 18541-2024 artfynd.xlsx
+++ b/artfynd/A 18541-2024 artfynd.xlsx
@@ -2706,10 +2706,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118000752</v>
+        <v>121391835</v>
       </c>
       <c r="B19" t="n">
-        <v>102054</v>
+        <v>102286</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>6360659</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2783,6 +2783,11 @@
           <t>Fröjel</t>
         </is>
       </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>I-Got-1588</t>
+        </is>
+      </c>
       <c r="Y19" t="inlineStr">
         <is>
           <t>2024-06-24</t>
@@ -2795,7 +2800,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2 m hög, nedliggande, överkörd.</t>
+          <t>1 träd (2 m), men nedliggande överkörd!</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2806,16 +2811,11 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Barrskog med lundstarr.</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Bengt Carlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -2823,7 +2823,11 @@
           <t>Jörgen Petersson</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">

--- a/artfynd/A 18541-2024 artfynd.xlsx
+++ b/artfynd/A 18541-2024 artfynd.xlsx
@@ -2709,7 +2709,7 @@
         <v>121391835</v>
       </c>
       <c r="B19" t="n">
-        <v>102286</v>
+        <v>102296</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 18541-2024 artfynd.xlsx
+++ b/artfynd/A 18541-2024 artfynd.xlsx
@@ -2709,7 +2709,7 @@
         <v>121391835</v>
       </c>
       <c r="B19" t="n">
-        <v>102296</v>
+        <v>102309</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 18541-2024 artfynd.xlsx
+++ b/artfynd/A 18541-2024 artfynd.xlsx
@@ -2709,7 +2709,7 @@
         <v>121391835</v>
       </c>
       <c r="B19" t="n">
-        <v>102309</v>
+        <v>102310</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 18541-2024 artfynd.xlsx
+++ b/artfynd/A 18541-2024 artfynd.xlsx
@@ -2709,7 +2709,7 @@
         <v>121391835</v>
       </c>
       <c r="B19" t="n">
-        <v>102310</v>
+        <v>102313</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 18541-2024 artfynd.xlsx
+++ b/artfynd/A 18541-2024 artfynd.xlsx
@@ -2709,7 +2709,7 @@
         <v>121391835</v>
       </c>
       <c r="B19" t="n">
-        <v>102313</v>
+        <v>102319</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 18541-2024 artfynd.xlsx
+++ b/artfynd/A 18541-2024 artfynd.xlsx
@@ -2709,7 +2709,7 @@
         <v>121391835</v>
       </c>
       <c r="B19" t="n">
-        <v>102319</v>
+        <v>102320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 18541-2024 artfynd.xlsx
+++ b/artfynd/A 18541-2024 artfynd.xlsx
@@ -2709,11 +2709,11 @@
         <v>121391835</v>
       </c>
       <c r="B19" t="n">
-        <v>102328</v>
+        <v>102612</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">

--- a/artfynd/A 18541-2024 artfynd.xlsx
+++ b/artfynd/A 18541-2024 artfynd.xlsx
@@ -2709,7 +2709,7 @@
         <v>121391835</v>
       </c>
       <c r="B19" t="n">
-        <v>102612</v>
+        <v>102630</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 18541-2024 artfynd.xlsx
+++ b/artfynd/A 18541-2024 artfynd.xlsx
@@ -2709,7 +2709,7 @@
         <v>121391835</v>
       </c>
       <c r="B19" t="n">
-        <v>102630</v>
+        <v>102632</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 18541-2024 artfynd.xlsx
+++ b/artfynd/A 18541-2024 artfynd.xlsx
@@ -2709,7 +2709,7 @@
         <v>121391835</v>
       </c>
       <c r="B19" t="n">
-        <v>102632</v>
+        <v>102207</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 18541-2024 artfynd.xlsx
+++ b/artfynd/A 18541-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118000831</v>
+        <v>118000832</v>
       </c>
       <c r="B2" t="n">
-        <v>57659</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57247</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100038</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698109</v>
+        <v>698134</v>
       </c>
       <c r="R2" t="n">
-        <v>6360613</v>
+        <v>6360639</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -791,47 +786,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118000737</v>
+        <v>118000780</v>
       </c>
       <c r="B3" t="n">
-        <v>97868</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219862</v>
+        <v>101242</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -840,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698100</v>
+        <v>698230</v>
       </c>
       <c r="R3" t="n">
-        <v>6360609</v>
+        <v>6360781</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -907,15 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118000792</v>
+        <v>118000781</v>
       </c>
       <c r="B4" t="n">
-        <v>42955</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,13 +961,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698134</v>
+        <v>698223</v>
       </c>
       <c r="R4" t="n">
-        <v>6360639</v>
+        <v>6360777</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1036,12 +1031,7 @@
         <v>118000782</v>
       </c>
       <c r="B5" t="n">
-        <v>42955</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,15 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118000795</v>
+        <v>118000783</v>
       </c>
       <c r="B6" t="n">
-        <v>42955</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,7 +1179,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1218,13 +1203,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698185</v>
+        <v>698216</v>
       </c>
       <c r="R6" t="n">
-        <v>6360629</v>
+        <v>6360742</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1267,7 +1252,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Glänta i kalkbarrskog.</t>
+          <t>Barrskog med lundstarr.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1285,15 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118000786</v>
+        <v>118000785</v>
       </c>
       <c r="B7" t="n">
-        <v>42955</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,10 +1324,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698159</v>
+        <v>698174</v>
       </c>
       <c r="R7" t="n">
-        <v>6360654</v>
+        <v>6360672</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1411,15 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118000753</v>
+        <v>118000786</v>
       </c>
       <c r="B8" t="n">
-        <v>108714</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,34 +1402,53 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698154</v>
+        <v>698159</v>
       </c>
       <c r="R8" t="n">
-        <v>6360659</v>
+        <v>6360654</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1518,37 +1512,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118000749</v>
+        <v>118000787</v>
       </c>
       <c r="B9" t="n">
-        <v>97764</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223591</v>
+        <v>101242</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1558,7 +1547,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1567,10 +1566,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698144</v>
+        <v>698045</v>
       </c>
       <c r="R9" t="n">
-        <v>6360649</v>
+        <v>6360718</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1634,15 +1633,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118000785</v>
+        <v>118000790</v>
       </c>
       <c r="B10" t="n">
-        <v>42955</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,7 +1663,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1693,10 +1687,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698174</v>
+        <v>698064</v>
       </c>
       <c r="R10" t="n">
-        <v>6360672</v>
+        <v>6360688</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1760,15 +1754,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118000721</v>
+        <v>118000791</v>
       </c>
       <c r="B11" t="n">
-        <v>108714</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1776,34 +1765,53 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>698064</v>
+        <v>698105</v>
       </c>
       <c r="R11" t="n">
-        <v>6360663</v>
+        <v>6360598</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1836,11 +1844,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1872,15 +1875,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118000746</v>
+        <v>118000792</v>
       </c>
       <c r="B12" t="n">
-        <v>108714</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1888,24 +1886,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
@@ -1979,15 +1996,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118000794</v>
+        <v>118000793</v>
       </c>
       <c r="B13" t="n">
-        <v>42955</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2038,10 +2050,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>698154</v>
+        <v>698144</v>
       </c>
       <c r="R13" t="n">
-        <v>6360659</v>
+        <v>6360649</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2074,6 +2086,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Troligen nytt ex.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2105,15 +2122,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118000783</v>
+        <v>118000794</v>
       </c>
       <c r="B14" t="n">
-        <v>42955</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,13 +2176,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>698216</v>
+        <v>698154</v>
       </c>
       <c r="R14" t="n">
-        <v>6360742</v>
+        <v>6360659</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2231,47 +2243,52 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118000832</v>
+        <v>118000795</v>
       </c>
       <c r="B15" t="n">
-        <v>56601</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100038</v>
+        <v>101242</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2280,13 +2297,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>698134</v>
+        <v>698185</v>
       </c>
       <c r="R15" t="n">
-        <v>6360639</v>
+        <v>6360629</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2329,7 +2346,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Barrskog med lundstarr.</t>
+          <t>Glänta i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2347,15 +2364,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118000790</v>
+        <v>118000796</v>
       </c>
       <c r="B16" t="n">
-        <v>42955</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43467</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2382,7 +2394,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2406,10 +2418,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>698064</v>
+        <v>698170</v>
       </c>
       <c r="R16" t="n">
-        <v>6360688</v>
+        <v>6360604</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2455,7 +2467,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Barrskog med lundstarr.</t>
+          <t>Skogskant.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2473,37 +2485,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118000781</v>
+        <v>118000831</v>
       </c>
       <c r="B17" t="n">
-        <v>42955</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>101242</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2511,19 +2518,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>friflygande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2532,13 +2529,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>698223</v>
+        <v>698109</v>
       </c>
       <c r="R17" t="n">
-        <v>6360777</v>
+        <v>6360613</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2599,53 +2596,57 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118000727</v>
+        <v>118000681</v>
       </c>
       <c r="B18" t="n">
-        <v>108714</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>698075</v>
+        <v>698088</v>
       </c>
       <c r="R18" t="n">
-        <v>6360628</v>
+        <v>6360723</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2706,42 +2707,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121391835</v>
+        <v>118000737</v>
       </c>
       <c r="B19" t="n">
-        <v>102229</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6037533</v>
+        <v>219862</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garderönn</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sorbus atrata</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Hedrén &amp; J.Levin</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2755,13 +2751,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>698154</v>
+        <v>698100</v>
       </c>
       <c r="R19" t="n">
-        <v>6360659</v>
+        <v>6360609</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2783,11 +2779,6 @@
           <t>Fröjel</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>I-Got-1588</t>
-        </is>
-      </c>
       <c r="Y19" t="inlineStr">
         <is>
           <t>2024-06-24</t>
@@ -2798,11 +2789,6 @@
           <t>2024-06-24</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>1 träd (2 m), men nedliggande överkörd!</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2811,11 +2797,16 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Barrskog med lundstarr.</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bengt Carlsson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -2823,23 +2814,14 @@
           <t>Jörgen Petersson</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118000791</v>
+        <v>118000657</v>
       </c>
       <c r="B20" t="n">
-        <v>42955</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2847,53 +2829,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>101242</v>
+        <v>220164</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
+          <t>Fröjel Stora Hajdes NR, Gtl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>698105</v>
+        <v>698230</v>
       </c>
       <c r="R20" t="n">
-        <v>6360598</v>
+        <v>6360795</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2928,6 +2891,11 @@
           <t>2024-06-24</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Plockhuggning hade skett med grova körspår!</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2939,7 +2907,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Barrskog med lundstarr.</t>
+          <t>Barrskog, betad i glänta.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2957,15 +2925,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118000793</v>
+        <v>118000721</v>
       </c>
       <c r="B21" t="n">
-        <v>42955</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2973,53 +2936,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>698144</v>
+        <v>698064</v>
       </c>
       <c r="R21" t="n">
-        <v>6360649</v>
+        <v>6360663</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3056,7 +3000,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Troligen nytt ex.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3088,15 +3032,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118000780</v>
+        <v>118000727</v>
       </c>
       <c r="B22" t="n">
-        <v>42955</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3104,56 +3043,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>698230</v>
+        <v>698075</v>
       </c>
       <c r="R22" t="n">
-        <v>6360781</v>
+        <v>6360628</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3211,6 +3131,548 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>118000746</v>
+      </c>
+      <c r="B23" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>698134</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6360639</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Barrskog med lundstarr.</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>118000753</v>
+      </c>
+      <c r="B24" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>698154</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6360659</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Barrskog med lundstarr.</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>118000658</v>
+      </c>
+      <c r="B25" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Fröjel Stora Hajdes NR, Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>698230</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6360795</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Plockhuggning hade skett med grova körspår!</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Barrskog, betad i glänta.</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>118000749</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>698144</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6360649</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Barrskog med lundstarr.</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121391835</v>
+      </c>
+      <c r="B27" t="n">
+        <v>103306</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6037533</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garderönn</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sorbus atrata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Hedrén &amp; J.Levin</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Fröjel Lilla Hajdes 2:1, Rumhagen, Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>698154</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6360659</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Fröjel</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>I-Got-1588-biogeo</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1 träd (2 m), men nedliggande överkörd!</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Bengt Carlsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18541-2024 artfynd.xlsx
+++ b/artfynd/A 18541-2024 artfynd.xlsx
@@ -3559,7 +3559,7 @@
         <v>121391835</v>
       </c>
       <c r="B27" t="n">
-        <v>103306</v>
+        <v>103385</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 18541-2024 artfynd.xlsx
+++ b/artfynd/A 18541-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118000832</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118000780</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,6 +1040,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118000781</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1146,6 +1166,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118000782</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1267,6 +1292,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118000783</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1388,6 +1418,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118000785</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1509,6 +1544,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118000786</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1630,6 +1670,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118000787</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1751,6 +1796,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118000790</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1872,6 +1922,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118000791</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1993,6 +2048,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118000792</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2119,6 +2179,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118000793</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2240,6 +2305,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118000794</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2361,6 +2431,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118000795</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2482,6 +2557,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118000796</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2593,6 +2673,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118000831</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2704,6 +2789,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118000681</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2815,6 +2905,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118000737</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2922,6 +3017,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118000657</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3029,6 +3129,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118000721</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3131,6 +3236,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118000727</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3233,6 +3343,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118000746</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3335,6 +3450,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118000753</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3442,6 +3562,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118000658</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3553,6 +3678,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118000749</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3673,8 +3803,41 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121391835</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>